--- a/www/download/IND.surplus_value.empe.r.pc.WIOD16.xlsx
+++ b/www/download/IND.surplus_value.empe.r.pc.WIOD16.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>80.48</t>
+          <t>0.804922934167377</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>0.867452689676561</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>69.23</t>
+          <t>0.692580147463171</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>45.75</t>
+          <t>0.457738145581079</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>33.63</t>
+          <t>0.336481113770164</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>30.36</t>
+          <t>0.303716387995782</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>37.25</t>
+          <t>0.372538343699666</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>33.17</t>
+          <t>0.331937556950152</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>47.36</t>
+          <t>0.473651112800749</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>46.67</t>
+          <t>0.466734611608086</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>37.95</t>
+          <t>0.379754287399527</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>0.246931860904809</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>29.14</t>
+          <t>0.291479677751621</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>28.75</t>
+          <t>0.287577736962823</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>32.22</t>
+          <t>0.322116088338584</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>77.87</t>
+          <t>0.778807330063946</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>83.09</t>
+          <t>0.830884802674171</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>85.08</t>
+          <t>0.851067021744579</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>74.57</t>
+          <t>0.745996367948976</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>73.71</t>
+          <t>0.737246642044403</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>78.11</t>
+          <t>0.780972360288232</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>72.49</t>
+          <t>0.724954245161448</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>75.78</t>
+          <t>0.758349534314002</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>78.06</t>
+          <t>0.780881405398403</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>76.02</t>
+          <t>0.760324575705138</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>84.75</t>
+          <t>0.847804246481324</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>81.45</t>
+          <t>0.814800768902038</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>77.98</t>
+          <t>0.77988735275865</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>64.55</t>
+          <t>0.645531660273274</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>66.24</t>
+          <t>0.662407420154522</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-30.59</t>
+          <t>-0.305815541552441</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-31.34</t>
+          <t>-0.313342158500252</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-34.27</t>
+          <t>-0.342574234942642</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>-41.9</t>
+          <t>-0.418945793265086</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-46.24</t>
+          <t>-0.462393450081993</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>-43.97</t>
+          <t>-0.439732109551219</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>-40.56</t>
+          <t>-0.405600859391087</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>-38.58</t>
+          <t>-0.385733838417908</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>-37.02</t>
+          <t>-0.370123253734917</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>-32.43</t>
+          <t>-0.32422265973251</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>-9.6</t>
+          <t>-0.0958980289426693</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>-10.8</t>
+          <t>-0.107841954842347</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>-5.55</t>
+          <t>-0.0554301244526674</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>-11.94</t>
+          <t>-0.119409766381195</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>-15.73</t>
+          <t>-0.15772070216777</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>197.71</t>
+          <t>1.97716901022775</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>202.97</t>
+          <t>2.02987946520875</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>209.69</t>
+          <t>2.09706523428608</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>215.37</t>
+          <t>2.15379425958935</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>234.91</t>
+          <t>2.34910504001984</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>250.52</t>
+          <t>2.50522537412282</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>247.04</t>
+          <t>2.47061986026076</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>279.11</t>
+          <t>2.79139073743089</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>290.37</t>
+          <t>2.90359567189252</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>243.3</t>
+          <t>2.43314852191965</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>268.15</t>
+          <t>2.68174552066402</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>283.46</t>
+          <t>2.83497867143826</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>267.26</t>
+          <t>2.67279875577076</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>252.91</t>
+          <t>2.52907810609562</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>217.62</t>
+          <t>2.17607317150225</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>311.95</t>
+          <t>3.11960359424383</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>345.87</t>
+          <t>3.45894643591509</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>349.69</t>
+          <t>3.49719334924498</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>365.05</t>
+          <t>3.65060149261026</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>372.73</t>
+          <t>3.7273597419506</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>359.19</t>
+          <t>3.59203532515965</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>359.76</t>
+          <t>3.59784331543596</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>369.38</t>
+          <t>3.69412251266696</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>343.01</t>
+          <t>3.43027630319028</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>316.59</t>
+          <t>3.16604263602853</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>305.4</t>
+          <t>3.05435759779085</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>311.39</t>
+          <t>3.1144247850717</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>313.36</t>
+          <t>3.13384603667665</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>329.32</t>
+          <t>3.29321183001084</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>321.64</t>
+          <t>3.21634610467908</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>72.19</t>
+          <t>0.722035197029665</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>71.04</t>
+          <t>0.710724387657691</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>64.03</t>
+          <t>0.640572538271543</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>53.91</t>
+          <t>0.539335955802536</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>47.45</t>
+          <t>0.474629439110883</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>42.88</t>
+          <t>0.428960854456034</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>40.41</t>
+          <t>0.404108014993725</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>0.479234767015691</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>57.73</t>
+          <t>0.577434078462356</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>0.566159520264407</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>63.69</t>
+          <t>0.637143307476134</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>54.18</t>
+          <t>0.542198027936275</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>55.56</t>
+          <t>0.555751183854649</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>57.91</t>
+          <t>0.579126234920679</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>67.68</t>
+          <t>0.676706279873899</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-0.0368939807789499</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0.0300937342247858</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0.0700879959034557</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>16.28</t>
+          <t>0.162840781554543</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>0.213559200069142</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>29.33</t>
+          <t>0.293339030298541</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>28.11</t>
+          <t>0.281146539832267</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>37.04</t>
+          <t>0.370448862308038</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>30.8</t>
+          <t>0.307996005920808</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>0.266017762842506</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>0.299075675978803</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>35.59</t>
+          <t>0.356043197712259</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>32.55</t>
+          <t>0.325549668660983</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>39.77</t>
+          <t>0.397736580810075</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>42.11</t>
+          <t>0.42109228831731</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>66.77</t>
+          <t>0.667805278987949</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>53.88</t>
+          <t>0.539054331238494</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>30.04</t>
+          <t>0.300560194072099</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>15.11</t>
+          <t>0.151206842545538</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>17.48</t>
+          <t>0.174838517514948</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>23.07</t>
+          <t>0.230728649544169</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>38.45</t>
+          <t>0.384568174766494</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>47.12</t>
+          <t>0.471392440776163</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>33.9</t>
+          <t>0.33902623282838</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>50.92</t>
+          <t>0.509288832299474</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>50.86</t>
+          <t>0.508744190464347</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>55.97</t>
+          <t>0.559902585958696</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>66.2</t>
+          <t>0.662053092477175</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>60.08</t>
+          <t>0.600796225428825</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>60.14</t>
+          <t>0.601364285020774</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>357.55</t>
+          <t>3.57557473299489</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>333.94</t>
+          <t>3.33955942321326</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>302.12</t>
+          <t>3.02183134022146</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>265.62</t>
+          <t>2.65660332212955</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>261.53</t>
+          <t>2.61526605156286</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>252.53</t>
+          <t>2.52538409323822</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>256.82</t>
+          <t>2.5682459420996</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>256.43</t>
+          <t>2.56493246768976</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>252.86</t>
+          <t>2.52899816361851</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>269.59</t>
+          <t>2.69677038748684</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>277.74</t>
+          <t>2.77663741023562</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>253.88</t>
+          <t>2.53944852230957</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>272.05</t>
+          <t>2.71885580777247</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>255.93</t>
+          <t>2.56017973551843</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>269.72</t>
+          <t>2.69498970320848</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>24.27</t>
+          <t>0.243155199115278</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>28.13</t>
+          <t>0.280577907194741</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>26.29</t>
+          <t>0.263629155031037</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>12.31</t>
+          <t>0.123788109817437</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>9.13</t>
+          <t>0.090516925196042</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>11.43</t>
+          <t>0.113809108552525</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>11.36</t>
+          <t>0.113755970510203</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>12.97</t>
+          <t>0.130726954546915</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>17.19</t>
+          <t>0.172173333365654</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>17.74</t>
+          <t>0.177417931349084</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>32.19</t>
+          <t>0.321971019160736</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>23.48</t>
+          <t>0.23492505155026</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>32.51</t>
+          <t>0.325187655669721</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>0.208005326646737</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>21.32</t>
+          <t>0.213149685033944</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>21.94</t>
+          <t>0.219484565444642</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>0.202600496191374</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>0.190946827270379</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.00632768294576391</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>0.0197704505459007</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>0.0102518025883036</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>0.0558820852097119</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>9.91</t>
+          <t>0.0992826969085283</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>8.9</t>
+          <t>0.0890753212161983</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>12.99</t>
+          <t>0.129952694972543</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>0.182127046962246</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>21.86</t>
+          <t>0.218736721194582</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>29.76</t>
+          <t>0.297705857452606</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>45.25</t>
+          <t>0.452489349294308</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>38.04</t>
+          <t>0.380399702555005</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>88.72</t>
+          <t>0.88741802208925</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>84.57</t>
+          <t>0.845899588321631</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>76.84</t>
+          <t>0.768525648339563</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>63.65</t>
+          <t>0.636658362281899</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>0.535020511849507</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>54.6</t>
+          <t>0.546011976407176</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>58.89</t>
+          <t>0.588945810342436</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>59.48</t>
+          <t>0.59491858985563</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>55.63</t>
+          <t>0.556331760921034</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>64.41</t>
+          <t>0.644161098050976</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>76.18</t>
+          <t>0.761905539802071</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>0.727019767547139</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>85.52</t>
+          <t>0.855121308285613</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>75.51</t>
+          <t>0.755030014380624</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>72.99</t>
+          <t>0.729773745909064</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>239.3</t>
+          <t>2.39346412218372</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>254.75</t>
+          <t>2.54823364164543</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>187.39</t>
+          <t>1.87447895588757</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>154.07</t>
+          <t>1.54152468629346</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>167.73</t>
+          <t>1.67793409926833</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>177.44</t>
+          <t>1.77466742022312</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>137.05</t>
+          <t>1.37097654205051</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>127.59</t>
+          <t>1.27619700134348</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>120.15</t>
+          <t>1.20179935796324</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>151.39</t>
+          <t>1.51416237717099</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>178.75</t>
+          <t>1.78792555651426</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>173.32</t>
+          <t>1.73393515232683</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>176.12</t>
+          <t>1.76138555610089</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>172.65</t>
+          <t>1.72632990418486</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>1.38480136366305</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>78.14</t>
+          <t>0.782680164827781</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>81.52</t>
+          <t>0.816382605140653</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>74.56</t>
+          <t>0.746325899771191</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>57.31</t>
+          <t>0.573274901710928</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>48.98</t>
+          <t>0.489944433819385</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>45.28</t>
+          <t>0.45280322975382</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>49.95</t>
+          <t>0.498970645860548</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>52.99</t>
+          <t>0.530285979497219</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>47.93</t>
+          <t>0.479565614820466</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>60.98</t>
+          <t>0.609700404757711</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>78.81</t>
+          <t>0.788345759289402</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>86.32</t>
+          <t>0.863540787455387</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>77.01</t>
+          <t>0.770394331927178</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>72.21</t>
+          <t>0.722012231963816</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>81.21</t>
+          <t>0.811970032756567</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>27.65</t>
+          <t>0.276663779896549</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>25.94</t>
+          <t>0.259559846549244</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>14.91</t>
+          <t>0.149251969551157</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>0.0471314173741828</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>6.88</t>
+          <t>0.0688327668644435</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>7.47</t>
+          <t>0.0747642586926291</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>9.82</t>
+          <t>0.0982978081288117</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>0.142206162899013</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>0.174660943397491</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>24.08</t>
+          <t>0.240903209792108</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>0.402083281897906</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>31.98</t>
+          <t>0.319920646419602</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>0.390473131300679</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>33.68</t>
+          <t>0.336668655060023</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>0.291390605900415</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>36.28</t>
+          <t>0.362897178766156</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>28.23</t>
+          <t>0.282494569711855</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>20.61</t>
+          <t>0.206253476553537</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>17.53</t>
+          <t>0.175391099157466</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>8.24</t>
+          <t>0.0824869593882163</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>10.21</t>
+          <t>0.102150766399784</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>8.71</t>
+          <t>0.0871105134312267</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>0.17513667227291</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>31.73</t>
+          <t>0.317409298857996</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>41.8</t>
+          <t>0.418064652267788</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>58.16</t>
+          <t>0.581759071008095</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>62.77</t>
+          <t>0.627925795581359</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>63.33</t>
+          <t>0.633390159665465</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>0.434951747601899</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>76.06</t>
+          <t>0.760515291311159</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>126.74</t>
+          <t>1.26738455061588</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>134.24</t>
+          <t>1.34259423592076</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>124.35</t>
+          <t>1.24375347289029</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>107.39</t>
+          <t>1.07407993022205</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>104.37</t>
+          <t>1.04382960183458</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>98.92</t>
+          <t>0.98911864512432</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>94.67</t>
+          <t>0.946773702772757</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>95.41</t>
+          <t>0.954249838874724</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>97.95</t>
+          <t>0.979689315735046</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>99.12</t>
+          <t>0.991379330236961</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>117.71</t>
+          <t>1.17731649410884</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>115.57</t>
+          <t>1.15590702635725</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>145.67</t>
+          <t>1.45689214835022</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>150.52</t>
+          <t>1.50548439665708</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>142.69</t>
+          <t>1.4269838043891</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>252.17</t>
+          <t>2.52203824677423</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>243.62</t>
+          <t>2.43676251890909</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>223.22</t>
+          <t>2.23286049374859</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>209.6</t>
+          <t>2.09657323711591</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>234.63</t>
+          <t>2.34655287304165</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>255.98</t>
+          <t>2.55995041813555</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>272.64</t>
+          <t>2.72703235584329</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>288.35</t>
+          <t>2.88439493957836</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>293.97</t>
+          <t>2.93917357335594</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>303.4</t>
+          <t>3.03414338027953</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>321.12</t>
+          <t>3.21212436155964</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>322.05</t>
+          <t>3.22157228622954</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>342.69</t>
+          <t>3.42722089139118</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>343.44</t>
+          <t>3.4343224636836</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>327.68</t>
+          <t>3.27610448939426</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>140.94</t>
+          <t>1.40942098071756</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>143.97</t>
+          <t>1.43979723292757</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>151.09</t>
+          <t>1.51095744909872</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>114.81</t>
+          <t>1.14813745382295</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>123.59</t>
+          <t>1.23592746451693</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>108.14</t>
+          <t>1.0813815491375</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>106.53</t>
+          <t>1.06533826937984</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>100.12</t>
+          <t>1.00122614626902</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>106.77</t>
+          <t>1.06776767386544</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>95.76</t>
+          <t>0.957650824341928</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>106.73</t>
+          <t>1.06740123551755</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>112.11</t>
+          <t>1.12121575740442</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>119.62</t>
+          <t>1.19620860644298</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>126.81</t>
+          <t>1.26812690880613</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>128.29</t>
+          <t>1.28285643897239</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>134.92</t>
+          <t>1.34920945618851</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>140.39</t>
+          <t>1.40401440424936</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>143.56</t>
+          <t>1.43564891749511</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>145.55</t>
+          <t>1.455509952197</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>153.89</t>
+          <t>1.53893203374913</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>157.51</t>
+          <t>1.57514026856926</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>166.97</t>
+          <t>1.66976645186439</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>169.09</t>
+          <t>1.69099885986072</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>180.15</t>
+          <t>1.80139273856633</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>182.37</t>
+          <t>1.82370122503608</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>189.02</t>
+          <t>1.89028083176506</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>183.42</t>
+          <t>1.83437896810773</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>193.08</t>
+          <t>1.93087697326714</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>200.23</t>
+          <t>2.00229894640983</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>205.26</t>
+          <t>2.05252142820396</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>124.05</t>
+          <t>1.240742094007</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>88.35</t>
+          <t>0.88381727892687</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>0.778198702039121</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>79.87</t>
+          <t>0.798922210375401</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>57.17</t>
+          <t>0.571773066335131</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>50.34</t>
+          <t>0.503474615951017</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>48.79</t>
+          <t>0.487954434053911</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>53.04</t>
+          <t>0.530625685809164</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>51.93</t>
+          <t>0.51937261319612</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>79.28</t>
+          <t>0.792920758885877</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>176.98</t>
+          <t>1.77032977164488</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>97.63</t>
+          <t>0.976770238512307</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>110.63</t>
+          <t>1.10653953751905</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>106.05</t>
+          <t>1.06051570313522</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>125.62</t>
+          <t>1.2559320660643</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>84.15</t>
+          <t>0.841639030028478</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>80.29</t>
+          <t>0.803002778921019</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>73.91</t>
+          <t>0.739435058250548</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>58.31</t>
+          <t>0.583241996265242</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>48.43</t>
+          <t>0.484406903526881</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>49.22</t>
+          <t>0.492208937182249</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>45.39</t>
+          <t>0.453918705305924</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>55.77</t>
+          <t>0.557899207023187</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>55.11</t>
+          <t>0.551115458216968</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>67.08</t>
+          <t>0.670918267048185</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>0.735068773397229</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>70.46</t>
+          <t>0.704720376826934</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>89.19</t>
+          <t>0.891952642526701</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>89.53</t>
+          <t>0.895216961506812</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>86.54</t>
+          <t>0.865262405907649</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>29.1</t>
+          <t>0.290942588187761</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>34.34</t>
+          <t>0.344609329664747</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>38.25</t>
+          <t>0.383678311557949</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>34.17</t>
+          <t>0.342592136110057</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>30.48</t>
+          <t>0.305778900346032</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>31.27</t>
+          <t>0.313556278766498</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>36.76</t>
+          <t>0.366729641199491</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>56.52</t>
+          <t>0.565408752475151</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>59.17</t>
+          <t>0.591971780230051</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>59.31</t>
+          <t>0.591902839475845</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>65.65</t>
+          <t>0.656572125252409</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>51.18</t>
+          <t>0.513389776336503</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>57.11</t>
+          <t>0.572443684759734</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>68.05</t>
+          <t>0.681239610503914</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>69.18</t>
+          <t>0.693437730892301</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>77.77</t>
+          <t>0.777763205106117</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>72.29</t>
+          <t>0.723486317035985</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>66.59</t>
+          <t>0.666321558725262</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>59.23</t>
+          <t>0.592474175488391</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>57.61</t>
+          <t>0.576377911641383</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>56.85</t>
+          <t>0.568585328947932</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>56.19</t>
+          <t>0.561973495775429</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>64.12</t>
+          <t>0.641621785475588</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>69.64</t>
+          <t>0.696298033640391</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>82.72</t>
+          <t>0.827277636001605</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>84.63</t>
+          <t>0.846632794618239</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>77.12</t>
+          <t>0.771738523592509</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>69.04</t>
+          <t>0.690612118367607</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>64.49</t>
+          <t>0.644901426457079</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>61.44</t>
+          <t>0.614187718495794</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>145.29</t>
+          <t>1.45273969249036</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>137.45</t>
+          <t>1.37502654578555</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>125.13</t>
+          <t>1.25143678923551</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>107.7</t>
+          <t>1.07676806948554</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>138.38</t>
+          <t>1.38369649212211</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>136.69</t>
+          <t>1.36739314468028</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>110.27</t>
+          <t>1.10318590214622</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>135.67</t>
+          <t>1.35718940870863</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>128.41</t>
+          <t>1.28414862796083</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>148.43</t>
+          <t>1.48425058506461</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>193.47</t>
+          <t>1.9350396472972</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>163.75</t>
+          <t>1.6378283763022</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>171.11</t>
+          <t>1.71048049591549</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>147.8</t>
+          <t>1.47734643671641</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>133.14</t>
+          <t>1.33120471849272</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>49.95</t>
+          <t>0.49972364121865</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>51.61</t>
+          <t>0.516170678317366</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>43.49</t>
+          <t>0.435267714507765</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>37.55</t>
+          <t>0.375902421110238</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>30.16</t>
+          <t>0.301588105230318</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>21.86</t>
+          <t>0.218557838193709</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>0.175045610816186</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>31.07</t>
+          <t>0.311134530066055</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>5.19</t>
+          <t>0.0519824230410992</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>-7.24</t>
+          <t>-0.0722947336212627</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>-3.4</t>
+          <t>-0.0338843523192978</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>-6.02</t>
+          <t>-0.0600243739832741</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>0.0354225409876079</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>0.0390526986556985</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.00106456240358321</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>166.17</t>
+          <t>1.66182633230761</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>167.54</t>
+          <t>1.67566498279283</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>174.86</t>
+          <t>1.74881348145231</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>160.52</t>
+          <t>1.60534121281256</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>164.33</t>
+          <t>1.64332955246482</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>161.41</t>
+          <t>1.6142285190088</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>136.74</t>
+          <t>1.36759769525649</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>121.59</t>
+          <t>1.21611879759963</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>136.14</t>
+          <t>1.36140131041637</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>171.44</t>
+          <t>1.71445504428871</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>225.78</t>
+          <t>2.25827005729685</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>217.15</t>
+          <t>2.172135723814</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>219.24</t>
+          <t>2.19244032616903</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>220.6</t>
+          <t>2.20598133581068</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>192.91</t>
+          <t>1.92884833674581</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>312.38</t>
+          <t>3.12397137066367</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>278.56</t>
+          <t>2.7859710155636</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>263.34</t>
+          <t>2.63376783907805</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>295.64</t>
+          <t>2.95663892741014</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>324.39</t>
+          <t>3.24403629729993</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>325.94</t>
+          <t>3.25960931851386</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>337.82</t>
+          <t>3.37848496299597</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>347.74</t>
+          <t>3.47794072796106</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>371.79</t>
+          <t>3.71789111874554</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>367.85</t>
+          <t>3.67861352516617</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>378.07</t>
+          <t>3.78108696054093</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>387.42</t>
+          <t>3.87484451337393</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>389.56</t>
+          <t>3.89578116808909</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>375.48</t>
+          <t>3.75486126535704</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>380.13</t>
+          <t>3.80119790972404</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>162.17</t>
+          <t>1.62186494475148</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>143.73</t>
+          <t>1.43758100847182</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>139.63</t>
+          <t>1.39674735902078</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>102.91</t>
+          <t>1.029232785797</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>104.21</t>
+          <t>1.04209040397453</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>94.78</t>
+          <t>0.94787257613197</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>99.64</t>
+          <t>0.996488460973414</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>111.59</t>
+          <t>1.11631053045091</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>98.46</t>
+          <t>0.984877002403429</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>108.26</t>
+          <t>1.0827514726499</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>126.32</t>
+          <t>1.26354379209573</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>124.48</t>
+          <t>1.24528396626432</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>120.17</t>
+          <t>1.20195743245211</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>1.19994513019841</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>131.87</t>
+          <t>1.31855216828101</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-27.23</t>
+          <t>-0.272326334260384</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>-23.18</t>
+          <t>-0.231722829657109</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>-26.28</t>
+          <t>-0.262755051876437</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>-22.43</t>
+          <t>-0.224269803213305</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-19.01</t>
+          <t>-0.190073651317861</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>-15.82</t>
+          <t>-0.158190748481538</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>-16.21</t>
+          <t>-0.162102674921093</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>-17.38</t>
+          <t>-0.173743158643437</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>-21.36</t>
+          <t>-0.213604071377187</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>-12.43</t>
+          <t>-0.124364067167709</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>0.070849981116381</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>9.07</t>
+          <t>0.0908554652328548</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>14.57</t>
+          <t>0.145863911141362</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>-19.56</t>
+          <t>-0.195524260798179</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>-19.17</t>
+          <t>-0.191772069624856</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>205.42</t>
+          <t>2.05430480215516</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>166.52</t>
+          <t>1.665335680247</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>196.05</t>
+          <t>1.96065741475683</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>204.96</t>
+          <t>2.04974400295626</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>221.78</t>
+          <t>2.21785453450606</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>225.22</t>
+          <t>2.25223461565115</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>237.25</t>
+          <t>2.37261079436485</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>240.82</t>
+          <t>2.40854093153436</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>216.8</t>
+          <t>2.16803493867565</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>250.35</t>
+          <t>2.50360445025553</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>236.51</t>
+          <t>2.36541190940016</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>232.5</t>
+          <t>2.32539202656038</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>246.28</t>
+          <t>2.46291739295945</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>234.68</t>
+          <t>2.3467903904025</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>233.6</t>
+          <t>2.33578514343887</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>97.77</t>
+          <t>0.977768668696746</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>94.99</t>
+          <t>0.950048038104815</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>101.31</t>
+          <t>1.01328534567715</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>93.09</t>
+          <t>0.931019186395872</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>91.67</t>
+          <t>0.916668707809083</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>95.6</t>
+          <t>0.956050262150891</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>105.57</t>
+          <t>1.05583838518422</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>113.3</t>
+          <t>1.13309778301236</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>110.01</t>
+          <t>1.10016489550335</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>127.26</t>
+          <t>1.27276355197901</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>138.27</t>
+          <t>1.38296991358006</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>126.37</t>
+          <t>1.26396047965186</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>132.33</t>
+          <t>1.32340381987532</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>129.55</t>
+          <t>1.29543726298694</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>138.14</t>
+          <t>1.38114838745805</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>59.27</t>
+          <t>0.592752476660974</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>58.03</t>
+          <t>0.580385600768522</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>111.45</t>
+          <t>1.11457104395895</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>99.05</t>
+          <t>0.99056598661872</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>137.03</t>
+          <t>1.37033275031855</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>99.61</t>
+          <t>0.996106555399011</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>103.89</t>
+          <t>1.03908530477547</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>103.03</t>
+          <t>1.03050956141279</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>96.81</t>
+          <t>0.967899129259236</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>108.33</t>
+          <t>1.0833879211292</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>114.6</t>
+          <t>1.14615717247491</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>146.4</t>
+          <t>1.46414833375006</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>210.85</t>
+          <t>2.10855706110883</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>227.18</t>
+          <t>2.2717828847194</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>214.97</t>
+          <t>2.14963657792263</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>155.14</t>
+          <t>1.55147841313237</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>152.31</t>
+          <t>1.52333424052108</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>141.49</t>
+          <t>1.41513298601276</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>122.34</t>
+          <t>1.22350527572734</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>112.03</t>
+          <t>1.12036090825885</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>106.92</t>
+          <t>1.0692484220346</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>105.59</t>
+          <t>1.05604961015503</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>90.08</t>
+          <t>0.900944109769247</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>89.08</t>
+          <t>0.890597455062628</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>80.64</t>
+          <t>0.806452115275285</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>67.76</t>
+          <t>0.677694841867558</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>69.4</t>
+          <t>0.694146016437768</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>56.33</t>
+          <t>0.56340973328226</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>52.84</t>
+          <t>0.528433874623589</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>75.29</t>
+          <t>0.752846651374881</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>254.88</t>
+          <t>2.54891408485587</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>272.14</t>
+          <t>2.72207386258728</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>253.87</t>
+          <t>2.5390503993849</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>228.38</t>
+          <t>2.28338639765037</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>171.36</t>
+          <t>1.71336196186683</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>164.53</t>
+          <t>1.64533096402932</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>144.15</t>
+          <t>1.44158313280738</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>109.04</t>
+          <t>1.0896333145642</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>123.72</t>
+          <t>1.23706189683347</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>94.17</t>
+          <t>0.941770697254866</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>126.11</t>
+          <t>1.26152262498969</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>121.18</t>
+          <t>1.21229293380843</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>107.11</t>
+          <t>1.07117925879755</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>0.94400376945154</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>93.76</t>
+          <t>0.937438051680105</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>62.76</t>
+          <t>0.627674582239172</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>59.79</t>
+          <t>0.59783509949172</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>65.58</t>
+          <t>0.655923954134295</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>49.69</t>
+          <t>0.496992431509277</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>30.34</t>
+          <t>0.303260932535882</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>0.240387243764963</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>22.43</t>
+          <t>0.224334779848496</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>25.38</t>
+          <t>0.25405901488487</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>25.39</t>
+          <t>0.254083082301267</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>23.14</t>
+          <t>0.231609909980159</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>33.15</t>
+          <t>0.331708503976923</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>0.248799078725367</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>27.32</t>
+          <t>0.273379190846133</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>27.77</t>
+          <t>0.277732590928645</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>28.06</t>
+          <t>0.280538537851963</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>59.86</t>
+          <t>0.598823010070197</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>62.12</t>
+          <t>0.621596874598502</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>56.67</t>
+          <t>0.566851779921706</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>45.53</t>
+          <t>0.455548765487854</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>37.95</t>
+          <t>0.379635347861657</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>41.67</t>
+          <t>0.416830751300962</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>43.89</t>
+          <t>0.439008649914944</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>0.493568735793031</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>51.72</t>
+          <t>0.517290923213494</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>62.31</t>
+          <t>0.623219931487067</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>81.39</t>
+          <t>0.814352627140091</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>63.87</t>
+          <t>0.639097237179876</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>74.41</t>
+          <t>0.744205879295467</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>64.9</t>
+          <t>0.64910910809184</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>68.85</t>
+          <t>0.688106614228172</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>170.02</t>
+          <t>1.70036121203028</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>172.79</t>
+          <t>1.72817133430517</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>203.21</t>
+          <t>2.03241163580148</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>195.28</t>
+          <t>1.95296110781184</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>177.05</t>
+          <t>1.77057126383764</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>203.1</t>
+          <t>2.03106399111475</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>215.4</t>
+          <t>2.15432337543632</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>214.5</t>
+          <t>2.14540173884239</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>220.42</t>
+          <t>2.20398531547676</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>238.12</t>
+          <t>2.38143845430723</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>222.96</t>
+          <t>2.23025482606079</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>213.59</t>
+          <t>2.1366251593031</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>2.33048822887269</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>254.34</t>
+          <t>2.54325776776157</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>2.709184448163</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>25.67</t>
+          <t>0.256774815654722</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>21.43</t>
+          <t>0.214641915745794</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>15.86</t>
+          <t>0.158941452511857</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>15.38</t>
+          <t>0.153972568239041</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>18.39</t>
+          <t>0.18418083943819</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>19.66</t>
+          <t>0.196692889553402</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>23.35</t>
+          <t>0.233458028282702</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>32.78</t>
+          <t>0.328026909577188</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>39.93</t>
+          <t>0.399399571415374</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>41.8</t>
+          <t>0.417993511204094</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>44.48</t>
+          <t>0.444977652597432</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>46.07</t>
+          <t>0.461080546952298</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>50.93</t>
+          <t>0.509500081655223</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>59.55</t>
+          <t>0.595545866439862</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>51.68</t>
+          <t>0.516704327791146</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>55.38</t>
+          <t>0.554047914905593</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>51.75</t>
+          <t>0.517950403398646</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>45.71</t>
+          <t>0.457367577124695</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>41.65</t>
+          <t>0.416749475877396</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>0.408457789446607</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>40.06</t>
+          <t>0.400654554790252</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>44.04</t>
+          <t>0.440438612113108</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>56.08</t>
+          <t>0.561168741986857</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>65.85</t>
+          <t>0.658545723686534</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>0.717048197880992</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>77.66</t>
+          <t>0.777034950098691</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>77.62</t>
+          <t>0.777064183739381</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>77.65</t>
+          <t>0.776721239233506</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>83.98</t>
+          <t>0.839896735293653</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>0.842629811913633</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-3.51</t>
+          <t>-0.0350617039293791</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.00406885638859855</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-0.0238626690142154</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.00767733235843049</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>0.0825724627063193</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>0.0685656826045553</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>7.42</t>
+          <t>0.0741883187161527</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>15.68</t>
+          <t>0.156876002455217</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>18.89</t>
+          <t>0.188889561685891</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>19.49</t>
+          <t>0.194875035845896</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>26.06</t>
+          <t>0.260686741751302</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>34.21</t>
+          <t>0.342222900110043</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>0.357043519139798</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>40.13</t>
+          <t>0.401332498689111</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>43.36</t>
+          <t>0.43355324443708</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>34.73</t>
+          <t>0.347368100632875</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>37.58</t>
+          <t>0.375941757313781</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>36.28</t>
+          <t>0.362953078415819</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>38.31</t>
+          <t>0.383227449005872</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>43.02</t>
+          <t>0.430249686523956</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>44.22</t>
+          <t>0.442256553234493</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>45.12</t>
+          <t>0.451179932547898</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>53.52</t>
+          <t>0.53529115197188</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>54.71</t>
+          <t>0.547110005938695</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>54.15</t>
+          <t>0.541491150947524</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>60.02</t>
+          <t>0.60033297943096</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>63.38</t>
+          <t>0.634036260583436</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>64.59</t>
+          <t>0.645989717921544</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>69.93</t>
+          <t>0.699359973260164</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>74.01</t>
+          <t>0.740078758070218</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4337,84 +4342,84 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>127.05</t>
+          <t>1.27057613788164</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>137.31</t>
+          <t>1.37323094954575</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>118.03</t>
+          <t>1.18051334887666</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>119.82</t>
+          <t>1.19832810548764</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>102.69</t>
+          <t>1.02690352101827</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>101.39</t>
+          <t>1.01392881531493</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>95.85</t>
+          <t>0.958537219640494</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>90.96</t>
+          <t>0.909876320277995</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>84.78</t>
+          <t>0.847891455856336</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>95.84</t>
+          <t>0.958452572280511</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>105.51</t>
+          <t>1.05529962077495</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>109.37</t>
+          <t>1.09397155545113</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>121.22</t>
+          <t>1.21228658914285</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>139.45</t>
+          <t>1.39446335386965</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>163.31</t>
+          <t>1.63290505440566</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4424,84 +4429,84 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>26.54</t>
+          <t>0.265645858888321</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>29.07</t>
+          <t>0.290920691577562</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>26.82</t>
+          <t>0.268457723973418</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>0.195239405331617</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>26.75</t>
+          <t>0.267602364080331</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>27.36</t>
+          <t>0.273414726256148</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>28.68</t>
+          <t>0.286872430664798</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>36.56</t>
+          <t>0.366080954278783</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>33.2</t>
+          <t>0.331806904759044</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>38.14</t>
+          <t>0.381360397136195</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>36.94</t>
+          <t>0.369573607853922</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>26.14</t>
+          <t>0.2619306340263</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>28.75</t>
+          <t>0.287668504071017</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>22.58</t>
+          <t>0.225926251949442</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>23.12</t>
+          <t>0.230846536836633</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4511,84 +4516,84 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>11.08</t>
+          <t>0.110872424300082</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>5.09</t>
+          <t>0.0510746812996405</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.00428370757318053</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-0.0457694663033944</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>-9.35</t>
+          <t>-0.0934430054047491</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>-7.74</t>
+          <t>-0.0773439629191789</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>-8.64</t>
+          <t>-0.0863061254299633</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>-7.97</t>
+          <t>-0.0794705604808905</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>-6.31</t>
+          <t>-0.0631202561146296</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>-4.49</t>
+          <t>-0.0448245500813679</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>0.0547456807171329</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>-4.15</t>
+          <t>-0.0412811961059865</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>0.050734283054249</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>-4.64</t>
+          <t>-0.0463743840529302</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-0.0395355021910827</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4600,7 +4605,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4612,7 +4617,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4624,7 +4629,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4636,7 +4641,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4648,7 +4653,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4695,6 +4700,11 @@
           <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4729,6 +4739,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>WIOD16</t>
